--- a/Assets/EggRogue/Configs/Excel/EggRogue_Balance.xlsx
+++ b/Assets/EggRogue/Configs/Excel/EggRogue_Balance.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MiniGameExample\Assets\EggRogue\Configs\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3473352C-CD92-42D8-9605-590CD70BE101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E92FD8-2DCD-4FDC-A2DD-7AA9CC0C50C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="225" windowWidth="38640" windowHeight="20715" activeTab="6" xr2:uid="{BD38E421-D0F5-4413-AB74-14A7BC66D52F}"/>
+    <workbookView xWindow="38280" yWindow="225" windowWidth="38640" windowHeight="20715" activeTab="2" xr2:uid="{BD38E421-D0F5-4413-AB74-14A7BC66D52F}"/>
   </bookViews>
   <sheets>
     <sheet name="Level-Base" sheetId="2" r:id="rId1"/>
     <sheet name="Level-SpawnMix" sheetId="3" r:id="rId2"/>
     <sheet name="Level-CardWeight" sheetId="4" r:id="rId3"/>
-    <sheet name="EggRogue_Enemies" sheetId="5" r:id="rId4"/>
-    <sheet name="EggRogue_Characters" sheetId="6" r:id="rId5"/>
-    <sheet name="EggRogue_Weapons" sheetId="7" r:id="rId6"/>
-    <sheet name="EggRogue_Cards" sheetId="8" r:id="rId7"/>
+    <sheet name="Level-WeaponWeight" sheetId="9" r:id="rId4"/>
+    <sheet name="EggRogue_Enemies" sheetId="5" r:id="rId5"/>
+    <sheet name="EggRogue_Characters" sheetId="6" r:id="rId6"/>
+    <sheet name="EggRogue_Weapons" sheetId="7" r:id="rId7"/>
+    <sheet name="EggRogue_Cards" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="209">
   <si>
     <t>关卡编号</t>
   </si>
@@ -246,9 +247,6 @@
     <t>基础攻速</t>
   </si>
   <si>
-    <t>基础子弹速度</t>
-  </si>
-  <si>
     <t>基础攻击范围</t>
   </si>
   <si>
@@ -555,9 +553,6 @@
     <t>移速加成</t>
   </si>
   <si>
-    <t>子弹速度加成</t>
-  </si>
-  <si>
     <t>攻击范围加成</t>
   </si>
   <si>
@@ -567,49 +562,19 @@
     <t>全面强化</t>
   </si>
   <si>
-    <t>伤害 +3, 攻速 +0.5, 生命 +15</t>
-  </si>
-  <si>
     <t>力量提升</t>
   </si>
   <si>
-    <t>伤害 +1</t>
-  </si>
-  <si>
-    <t>子弹加速</t>
-  </si>
-  <si>
-    <t>子弹速度 +10</t>
-  </si>
-  <si>
     <t>射程提升</t>
   </si>
   <si>
-    <t>攻击范围 +2</t>
-  </si>
-  <si>
     <t>攻速提升</t>
   </si>
   <si>
-    <t>攻击速度 +1</t>
-  </si>
-  <si>
-    <t>极速射击</t>
-  </si>
-  <si>
-    <t>攻击速度 +2, 子弹速度 +5</t>
-  </si>
-  <si>
     <t>生命提升</t>
   </si>
   <si>
-    <t>最大生命值 +20</t>
-  </si>
-  <si>
     <t>移速提升</t>
-  </si>
-  <si>
-    <t>移动速度 +1</t>
   </si>
   <si>
     <t>star</t>
@@ -620,6 +585,81 @@
   <si>
     <t>权重和</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W_WeaponLv1</t>
+  </si>
+  <si>
+    <t>W_WeaponLv2</t>
+  </si>
+  <si>
+    <t>W_WeaponLv3</t>
+  </si>
+  <si>
+    <t>W_WeaponLv4</t>
+  </si>
+  <si>
+    <t>W_WeaponLv5</t>
+  </si>
+  <si>
+    <t>护甲减伤加成</t>
+  </si>
+  <si>
+    <t>护甲强化</t>
+  </si>
+  <si>
+    <t>基础护甲</t>
+  </si>
+  <si>
+    <t>基础闪避</t>
+  </si>
+  <si>
+    <t>基础奖励加成</t>
+  </si>
+  <si>
+    <t>基础暴击率</t>
+  </si>
+  <si>
+    <t>基础暴击伤害</t>
+  </si>
+  <si>
+    <t>幸运值</t>
+  </si>
+  <si>
+    <t>击退</t>
+  </si>
+  <si>
+    <t>闪避加成</t>
+  </si>
+  <si>
+    <t>关卡奖励加成</t>
+  </si>
+  <si>
+    <t>暴击率加成</t>
+  </si>
+  <si>
+    <t>暴击伤害加成</t>
+  </si>
+  <si>
+    <t>幸运加成</t>
+  </si>
+  <si>
+    <t>击退加成</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>关卡奖励</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
+    <t>幸运</t>
   </si>
 </sst>
 </file>
@@ -665,21 +705,43 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFC00000"/>
@@ -1076,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -1937,6 +1999,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DDB2A5-980D-41EE-B085-8F4D696CE354}">
   <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -2151,7 +2230,7 @@
         <v>49</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2160,6 +2239,36 @@
         <v>0</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6">
+        <v>0.5</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>0</v>
       </c>
     </row>
@@ -2171,7 +2280,7 @@
         <v>49</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2180,6 +2289,36 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7">
+        <v>0.5</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>0</v>
       </c>
     </row>
@@ -2191,7 +2330,7 @@
         <v>49</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2200,6 +2339,36 @@
         <v>0</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8">
+        <v>0.5</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>0</v>
       </c>
     </row>
@@ -2211,7 +2380,7 @@
         <v>49</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2220,6 +2389,36 @@
         <v>0</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9">
+        <v>0.5</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>0</v>
       </c>
     </row>
@@ -2231,7 +2430,7 @@
         <v>49</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2240,6 +2439,36 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10">
+        <v>0.5</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>0</v>
       </c>
     </row>
@@ -2251,7 +2480,7 @@
         <v>49</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2260,6 +2489,36 @@
         <v>0</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11">
+        <v>0.5</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>0</v>
       </c>
     </row>
@@ -2271,7 +2530,7 @@
         <v>49</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2280,6 +2539,36 @@
         <v>0</v>
       </c>
       <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12">
+        <v>0.5</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>0</v>
       </c>
     </row>
@@ -2291,7 +2580,7 @@
         <v>49</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2300,6 +2589,36 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>0</v>
       </c>
     </row>
@@ -2311,7 +2630,7 @@
         <v>49</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2320,6 +2639,36 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
+        <v>0.5</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>0</v>
       </c>
     </row>
@@ -2331,7 +2680,7 @@
         <v>49</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2340,6 +2689,36 @@
         <v>0</v>
       </c>
       <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15">
+        <v>0.5</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>0</v>
       </c>
     </row>
@@ -2351,7 +2730,7 @@
         <v>49</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -2362,8 +2741,38 @@
       <c r="F16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16">
+        <v>0.5</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2371,7 +2780,7 @@
         <v>49</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2382,8 +2791,38 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17">
+        <v>0.5</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2391,7 +2830,7 @@
         <v>49</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2402,8 +2841,38 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18">
+        <v>0.5</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2411,7 +2880,7 @@
         <v>49</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2422,8 +2891,38 @@
       <c r="F19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19">
+        <v>0.5</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2431,7 +2930,7 @@
         <v>49</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2442,8 +2941,38 @@
       <c r="F20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20">
+        <v>0.5</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2451,7 +2980,7 @@
         <v>49</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2460,6 +2989,36 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>51</v>
+      </c>
+      <c r="M21">
+        <v>0.5</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
         <v>0</v>
       </c>
     </row>
@@ -2497,8 +3056,8 @@
       <c r="F1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>195</v>
+      <c r="G1" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -2984,11 +3543,12 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G2:G21">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="notEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="G2 G3:G21" formulaRange="1"/>
   </ignoredErrors>
@@ -2996,124 +3556,432 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66313595-DF38-4465-BDC3-974E3C5415DC}">
-  <dimension ref="A1:I4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7BEB81-B108-4A2D-8E5F-4374BA7F4936}">
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="6" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.6</v>
+      </c>
+      <c r="C2">
+        <v>0.4</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.6</v>
+      </c>
+      <c r="C3">
+        <v>0.4</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.4</v>
+      </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
+        <v>0.3</v>
+      </c>
+      <c r="D5">
+        <v>0.2</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.4</v>
+      </c>
+      <c r="C6">
+        <v>0.3</v>
+      </c>
+      <c r="D6">
+        <v>0.2</v>
+      </c>
+      <c r="E6">
+        <v>0.1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0.4</v>
+      </c>
+      <c r="C7">
+        <v>0.3</v>
+      </c>
+      <c r="D7">
+        <v>0.2</v>
+      </c>
+      <c r="E7">
+        <v>0.1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0.4</v>
+      </c>
+      <c r="C8">
+        <v>0.3</v>
+      </c>
+      <c r="D8">
+        <v>0.2</v>
+      </c>
+      <c r="E8">
+        <v>0.1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.3</v>
+      </c>
+      <c r="C9">
+        <v>0.3</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>0.2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0.3</v>
+      </c>
+      <c r="C10">
+        <v>0.3</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+      <c r="E10">
+        <v>0.2</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0.3</v>
+      </c>
+      <c r="C11">
+        <v>0.3</v>
+      </c>
+      <c r="D11">
+        <v>0.2</v>
+      </c>
+      <c r="E11">
+        <v>0.2</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>0.3</v>
+      </c>
+      <c r="C12">
+        <v>0.3</v>
+      </c>
+      <c r="D12">
+        <v>0.2</v>
+      </c>
+      <c r="E12">
+        <v>0.2</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0.3</v>
+      </c>
+      <c r="C13">
+        <v>0.3</v>
+      </c>
+      <c r="D13">
+        <v>0.2</v>
+      </c>
+      <c r="E13">
+        <v>0.1</v>
+      </c>
+      <c r="F13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>0.3</v>
+      </c>
+      <c r="C14">
+        <v>0.3</v>
+      </c>
+      <c r="D14">
+        <v>0.2</v>
+      </c>
+      <c r="E14">
+        <v>0.1</v>
+      </c>
+      <c r="F14">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0.3</v>
+      </c>
+      <c r="C15">
+        <v>0.3</v>
+      </c>
+      <c r="D15">
+        <v>0.2</v>
+      </c>
+      <c r="E15">
+        <v>0.1</v>
+      </c>
+      <c r="F15">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.3</v>
+      </c>
+      <c r="C16">
+        <v>0.3</v>
+      </c>
+      <c r="D16">
+        <v>0.2</v>
+      </c>
+      <c r="E16">
+        <v>0.1</v>
+      </c>
+      <c r="F16">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.2</v>
+      </c>
+      <c r="C17">
+        <v>0.2</v>
+      </c>
+      <c r="D17">
+        <v>0.2</v>
+      </c>
+      <c r="E17">
+        <v>0.2</v>
+      </c>
+      <c r="F17">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>0.2</v>
+      </c>
+      <c r="C18">
+        <v>0.2</v>
+      </c>
+      <c r="D18">
+        <v>0.2</v>
+      </c>
+      <c r="E18">
+        <v>0.2</v>
+      </c>
+      <c r="F18">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>0.2</v>
+      </c>
+      <c r="C19">
+        <v>0.2</v>
+      </c>
+      <c r="D19">
+        <v>0.2</v>
+      </c>
+      <c r="E19">
+        <v>0.2</v>
+      </c>
+      <c r="F19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>0.2</v>
+      </c>
+      <c r="C20">
+        <v>0.2</v>
+      </c>
+      <c r="D20">
+        <v>0.2</v>
+      </c>
+      <c r="E20">
+        <v>0.2</v>
+      </c>
+      <c r="F20">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3">
-        <v>60</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4">
-        <v>120</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
+      <c r="B21">
+        <v>0.2</v>
+      </c>
+      <c r="C21">
+        <v>0.2</v>
+      </c>
+      <c r="D21">
+        <v>0.2</v>
+      </c>
+      <c r="E21">
+        <v>0.2</v>
+      </c>
+      <c r="F21">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3123,743 +3991,129 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046C0161-2EF8-4240-A029-E45D60B0E0FA}">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66313595-DF38-4465-BDC3-974E3C5415DC}">
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" t="s">
-        <v>70</v>
-      </c>
       <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J1" t="s">
-        <v>72</v>
-      </c>
-      <c r="K1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2">
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
-      <c r="G2">
-        <v>10</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>21</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>0.5</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
       <c r="I3">
-        <v>19</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>20</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>0.5</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>0.5</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>0.5</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>20</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>0.5</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>0.5</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>23</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>24</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>0.5</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>20</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>0.5</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <v>18</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <v>0.5</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="I13">
-        <v>22</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
-      <c r="F14">
-        <v>0.5</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-      <c r="H14">
-        <v>10</v>
-      </c>
-      <c r="I14">
-        <v>20</v>
-      </c>
-      <c r="J14">
-        <v>2</v>
-      </c>
-      <c r="K14">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>0.5</v>
-      </c>
-      <c r="G15">
-        <v>10</v>
-      </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="I15">
-        <v>18</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <v>0.5</v>
-      </c>
-      <c r="G16">
-        <v>10</v>
-      </c>
-      <c r="H16">
-        <v>10</v>
-      </c>
-      <c r="I16">
-        <v>18</v>
-      </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-      <c r="K16">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-      <c r="F17">
-        <v>0.5</v>
-      </c>
-      <c r="G17">
-        <v>10</v>
-      </c>
-      <c r="H17">
-        <v>10</v>
-      </c>
-      <c r="I17">
-        <v>22</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-      <c r="F18">
-        <v>0.5</v>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-      <c r="H18">
-        <v>10</v>
-      </c>
-      <c r="I18">
-        <v>17</v>
-      </c>
-      <c r="J18">
-        <v>2</v>
-      </c>
-      <c r="K18">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>0.5</v>
-      </c>
-      <c r="G19">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>10</v>
-      </c>
-      <c r="I19">
-        <v>20</v>
-      </c>
-      <c r="J19">
-        <v>2</v>
-      </c>
-      <c r="K19">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>0.5</v>
-      </c>
-      <c r="G20">
-        <v>10</v>
-      </c>
-      <c r="H20">
-        <v>10</v>
-      </c>
-      <c r="I20">
-        <v>19</v>
-      </c>
-      <c r="J20">
-        <v>2</v>
-      </c>
-      <c r="K20">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>0.5</v>
-      </c>
-      <c r="G21">
-        <v>10</v>
-      </c>
-      <c r="H21">
-        <v>10</v>
-      </c>
-      <c r="I21">
-        <v>21</v>
-      </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
-      <c r="K21">
-        <v>1.5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3869,6 +4123,1136 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046C0161-2EF8-4240-A029-E45D60B0E0FA}">
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="97.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" t="s">
+        <v>191</v>
+      </c>
+      <c r="L1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M1" t="s">
+        <v>193</v>
+      </c>
+      <c r="N1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O1" t="s">
+        <v>195</v>
+      </c>
+      <c r="P1" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>0.5</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1.2</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1.5</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1.2</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1.5</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1.2</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1.5</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>1.2</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1.5</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>1.2</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>1.5</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>1.2</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>1.2</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>0.5</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1.5</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>1.2</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>0.5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>1.5</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>1.2</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>0.5</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>1.5</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>1.2</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>0.5</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>1.5</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1.2</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>0.5</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>1.5</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>1.2</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>0.5</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1.5</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1.2</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>0.5</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>1.5</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>1.2</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>0.5</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>1.5</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1.2</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>0.5</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>10</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>1.5</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>1.2</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>0.5</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>1.5</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1.2</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>0.5</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>10</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1.5</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>1.2</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>0.5</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>1.5</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>1.2</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>0.5</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>1.5</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1.2</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66DC5F04-4446-44A7-A3BD-06F6A27E2106}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3878,51 +5262,51 @@
         <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C1" t="s">
         <v>58</v>
       </c>
       <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" t="s">
         <v>135</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>138</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>139</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>140</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>141</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>142</v>
-      </c>
-      <c r="L1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" t="s">
         <v>144</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>145</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>146</v>
-      </c>
-      <c r="D2" t="s">
-        <v>147</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3946,24 +5330,24 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
         <v>148</v>
       </c>
-      <c r="B3" t="s">
-        <v>149</v>
-      </c>
       <c r="C3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" t="s">
         <v>146</v>
       </c>
-      <c r="D3" t="s">
-        <v>147</v>
-      </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -3975,7 +5359,7 @@
         <v>1.2</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>20</v>
@@ -3984,24 +5368,24 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" t="s">
         <v>150</v>
       </c>
-      <c r="B4" t="s">
-        <v>151</v>
-      </c>
       <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" t="s">
         <v>146</v>
       </c>
-      <c r="D4" t="s">
-        <v>147</v>
-      </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -4013,7 +5397,7 @@
         <v>1.2</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4">
         <v>20</v>
@@ -4022,24 +5406,24 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" t="s">
         <v>152</v>
       </c>
-      <c r="B5" t="s">
-        <v>153</v>
-      </c>
       <c r="C5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" t="s">
         <v>146</v>
       </c>
-      <c r="D5" t="s">
-        <v>147</v>
-      </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>16</v>
@@ -4051,7 +5435,7 @@
         <v>1.2</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J5">
         <v>20</v>
@@ -4060,24 +5444,24 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" t="s">
         <v>154</v>
       </c>
-      <c r="B6" t="s">
-        <v>155</v>
-      </c>
       <c r="C6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" t="s">
         <v>146</v>
       </c>
-      <c r="D6" t="s">
-        <v>147</v>
-      </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>50</v>
@@ -4089,7 +5473,7 @@
         <v>1.2</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>20</v>
@@ -4100,16 +5484,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" t="s">
         <v>156</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>157</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>158</v>
-      </c>
-      <c r="D7" t="s">
-        <v>159</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4133,24 +5517,24 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" t="s">
         <v>160</v>
       </c>
-      <c r="B8" t="s">
-        <v>161</v>
-      </c>
       <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
         <v>158</v>
       </c>
-      <c r="D8" t="s">
-        <v>159</v>
-      </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>12</v>
@@ -4159,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J8">
         <v>20</v>
@@ -4171,24 +5555,24 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
         <v>162</v>
       </c>
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
       <c r="C9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" t="s">
         <v>158</v>
       </c>
-      <c r="D9" t="s">
-        <v>159</v>
-      </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>18</v>
@@ -4197,10 +5581,10 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J9">
         <v>20</v>
@@ -4209,24 +5593,24 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" t="s">
         <v>164</v>
       </c>
-      <c r="B10" t="s">
-        <v>165</v>
-      </c>
       <c r="C10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" t="s">
         <v>158</v>
       </c>
-      <c r="D10" t="s">
-        <v>159</v>
-      </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>25</v>
@@ -4235,10 +5619,10 @@
         <v>12</v>
       </c>
       <c r="H10">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J10">
         <v>20</v>
@@ -4247,24 +5631,24 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" t="s">
         <v>166</v>
       </c>
-      <c r="B11" t="s">
-        <v>167</v>
-      </c>
       <c r="C11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" t="s">
         <v>158</v>
       </c>
-      <c r="D11" t="s">
-        <v>159</v>
-      </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>40</v>
@@ -4273,10 +5657,10 @@
         <v>24</v>
       </c>
       <c r="H11">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J11">
         <v>20</v>
@@ -4291,9 +5675,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8908E2A-303D-430B-A452-5B6C969D3564}">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -4302,56 +5686,71 @@
     <col min="9" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" t="s">
         <v>168</v>
-      </c>
-      <c r="B1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C1" t="s">
-        <v>169</v>
       </c>
       <c r="D1" t="s">
         <v>59</v>
       </c>
       <c r="E1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" t="s">
         <v>170</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>171</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>172</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1" t="s">
         <v>173</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>174</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M1" t="s">
+        <v>199</v>
+      </c>
+      <c r="N1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>175</v>
-      </c>
-      <c r="K1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>177</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0.5</v>
@@ -4366,33 +5765,48 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.2</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -4401,33 +5815,48 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4436,33 +5865,48 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.3</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -4471,33 +5915,48 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.3</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -4506,24 +5965,39 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4546,19 +6020,34 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4581,19 +6070,34 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -4616,19 +6120,34 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -4651,19 +6170,34 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -4686,19 +6220,34 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4713,27 +6262,42 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4751,24 +6315,39 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4786,24 +6365,39 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4821,24 +6415,39 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4856,24 +6465,39 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4888,27 +6512,42 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4923,27 +6562,42 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D19" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4958,27 +6612,42 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>183</v>
-      </c>
-      <c r="D20" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4993,27 +6662,42 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B21">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5028,97 +6712,142 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0.5</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>1</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>185</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>185</v>
-      </c>
-      <c r="D23" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
-      </c>
-      <c r="D24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5139,21 +6868,36 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1.5</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
-      </c>
-      <c r="D25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5174,21 +6918,36 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5209,27 +6968,42 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5238,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -5246,25 +7020,40 @@
       <c r="K27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
-      </c>
-      <c r="D28" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5281,25 +7070,40 @@
       <c r="K28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -5316,25 +7120,40 @@
       <c r="K29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5351,25 +7170,40 @@
       <c r="K30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -5386,19 +7220,34 @@
       <c r="K31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5421,19 +7270,34 @@
       <c r="K32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>189</v>
-      </c>
-      <c r="D33" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5456,19 +7320,34 @@
       <c r="K33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>189</v>
-      </c>
-      <c r="D34" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5491,19 +7370,34 @@
       <c r="K34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D35" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5526,19 +7420,34 @@
       <c r="K35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>189</v>
-      </c>
-      <c r="D36" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5561,19 +7470,34 @@
       <c r="K36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>191</v>
-      </c>
-      <c r="D37" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5596,19 +7520,34 @@
       <c r="K37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>191</v>
-      </c>
-      <c r="D38" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5631,19 +7570,34 @@
       <c r="K38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
-      </c>
-      <c r="D39" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5666,19 +7620,34 @@
       <c r="K39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
-      </c>
-      <c r="D40" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5701,19 +7670,34 @@
       <c r="K40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B41">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>191</v>
-      </c>
-      <c r="D41" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5736,19 +7720,37 @@
       <c r="K41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D42" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -5769,21 +7771,39 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -5804,21 +7824,39 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>10</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D44" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -5839,21 +7877,39 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>15</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D45" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -5874,21 +7930,39 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>20</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D46" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -5909,11 +7983,1375 @@
         <v>0</v>
       </c>
       <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>30</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>205</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>5</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>205</v>
+      </c>
+      <c r="D48" t="s">
+        <v>205</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>10</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49" t="s">
+        <v>205</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>15</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50" t="s">
+        <v>205</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>20</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>205</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>205</v>
+      </c>
+      <c r="D51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>30</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D52" t="s">
+        <v>206</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>5</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>206</v>
+      </c>
+      <c r="D53" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>10</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>206</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>206</v>
+      </c>
+      <c r="D54" t="s">
+        <v>206</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>15</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>206</v>
+      </c>
+      <c r="D55" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>20</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>206</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>206</v>
+      </c>
+      <c r="D56" t="s">
+        <v>206</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>30</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>207</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>207</v>
+      </c>
+      <c r="D57" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0.1</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>207</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D58" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0.2</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>207</v>
+      </c>
+      <c r="D59" t="s">
+        <v>207</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0.3</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>207</v>
+      </c>
+      <c r="D60" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0.4</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>207</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61" t="s">
+        <v>207</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0.5</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>208</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>208</v>
+      </c>
+      <c r="D62" t="s">
+        <v>208</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>2</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>208</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>208</v>
+      </c>
+      <c r="D63" t="s">
+        <v>208</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>4</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>208</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>6</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>208</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>208</v>
+      </c>
+      <c r="D65" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>208</v>
+      </c>
+      <c r="D66" t="s">
+        <v>208</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>12</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67" t="s">
+        <v>197</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>197</v>
+      </c>
+      <c r="D68" t="s">
+        <v>197</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>197</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" t="s">
+        <v>197</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" t="s">
+        <v>197</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" t="s">
+        <v>197</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E2:K41">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M29">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:Q71">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/EggRogue/Configs/Excel/EggRogue_Balance.xlsx
+++ b/Assets/EggRogue/Configs/Excel/EggRogue_Balance.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MiniGameExample\Assets\EggRogue\Configs\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E92FD8-2DCD-4FDC-A2DD-7AA9CC0C50C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69CFFA4-B8EF-494D-B170-52E5A4BA3BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="225" windowWidth="38640" windowHeight="20715" activeTab="2" xr2:uid="{BD38E421-D0F5-4413-AB74-14A7BC66D52F}"/>
+    <workbookView xWindow="38280" yWindow="225" windowWidth="38640" windowHeight="20715" activeTab="5" xr2:uid="{BD38E421-D0F5-4413-AB74-14A7BC66D52F}"/>
   </bookViews>
   <sheets>
     <sheet name="Level-Base" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="207">
   <si>
     <t>关卡编号</t>
   </si>
@@ -557,18 +557,6 @@
   </si>
   <si>
     <t>拾取范围加成</t>
-  </si>
-  <si>
-    <t>全面强化</t>
-  </si>
-  <si>
-    <t>力量提升</t>
-  </si>
-  <si>
-    <t>射程提升</t>
-  </si>
-  <si>
-    <t>攻速提升</t>
   </si>
   <si>
     <t>生命提升</t>
@@ -605,9 +593,6 @@
     <t>护甲减伤加成</t>
   </si>
   <si>
-    <t>护甲强化</t>
-  </si>
-  <si>
     <t>基础护甲</t>
   </si>
   <si>
@@ -650,9 +635,6 @@
     <t>闪避</t>
   </si>
   <si>
-    <t>关卡奖励</t>
-  </si>
-  <si>
     <t>暴击率</t>
   </si>
   <si>
@@ -660,6 +642,18 @@
   </si>
   <si>
     <t>幸运</t>
+  </si>
+  <si>
+    <t>增加基础伤害</t>
+  </si>
+  <si>
+    <t>护甲</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>每次通过关卡能获得的奖励</t>
   </si>
 </sst>
 </file>
@@ -716,15 +710,10 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -734,7 +723,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFC00000"/>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -1062,6 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9152D986-E313-4CED-977A-4EB568AB4D0D}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1997,6 +1987,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62DDB2A5-980D-41EE-B085-8F4D696CE354}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3030,6 +3021,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C677338C-E3BB-4CD3-9A77-6473BF43506F}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3057,7 +3049,7 @@
         <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -3543,7 +3535,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G2:G21">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3557,6 +3549,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7BEB81-B108-4A2D-8E5F-4374BA7F4936}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3569,19 +3562,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" t="s">
         <v>184</v>
-      </c>
-      <c r="C1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3992,6 +3985,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66313595-DF38-4465-BDC3-974E3C5415DC}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4124,6 +4118,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046C0161-2EF8-4240-A029-E45D60B0E0FA}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4165,25 +4160,25 @@
         <v>72</v>
       </c>
       <c r="K1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M1" t="s">
+        <v>188</v>
+      </c>
+      <c r="N1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" t="s">
+        <v>190</v>
+      </c>
+      <c r="P1" t="s">
         <v>191</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>192</v>
-      </c>
-      <c r="M1" t="s">
-        <v>193</v>
-      </c>
-      <c r="N1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O1" t="s">
-        <v>195</v>
-      </c>
-      <c r="P1" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -4203,7 +4198,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>10</v>
@@ -4256,7 +4251,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -4309,7 +4304,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -4362,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -4415,7 +4410,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -4468,7 +4463,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -4521,7 +4516,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -4574,7 +4569,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -4627,7 +4622,7 @@
         <v>5</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -4680,7 +4675,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -4733,7 +4728,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -4786,7 +4781,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -4839,7 +4834,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -4892,7 +4887,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -4945,7 +4940,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -4998,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -5051,7 +5046,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -5104,7 +5099,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -5157,7 +5152,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -5210,7 +5205,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -5254,6 +5249,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66DC5F04-4446-44A7-A3BD-06F6A27E2106}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -5677,7 +5673,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8908E2A-303D-430B-A452-5B6C969D3564}">
-  <dimension ref="A1:Q71"/>
+  <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -5691,7 +5688,7 @@
         <v>167</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C1" t="s">
         <v>168</v>
@@ -5712,7 +5709,7 @@
         <v>172</v>
       </c>
       <c r="I1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J1" t="s">
         <v>173</v>
@@ -5721,42 +5718,45 @@
         <v>174</v>
       </c>
       <c r="L1" t="s">
+        <v>193</v>
+      </c>
+      <c r="M1" t="s">
+        <v>194</v>
+      </c>
+      <c r="N1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O1" t="s">
+        <v>196</v>
+      </c>
+      <c r="P1" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q1" t="s">
         <v>198</v>
-      </c>
-      <c r="M1" t="s">
-        <v>199</v>
-      </c>
-      <c r="N1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>203</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5765,10 +5765,10 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -5791,22 +5791,25 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>137</v>
+      </c>
+      <c r="D3" t="s">
+        <v>203</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5815,10 +5818,10 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -5841,22 +5844,25 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>137</v>
+      </c>
+      <c r="D4" t="s">
+        <v>203</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5865,10 +5871,10 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -5891,22 +5897,25 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>137</v>
+      </c>
+      <c r="D5" t="s">
+        <v>203</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5915,10 +5924,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -5941,22 +5950,25 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>137</v>
+      </c>
+      <c r="D6" t="s">
+        <v>203</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -5965,10 +5977,10 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -5991,16 +6003,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -6012,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -6041,16 +6053,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -6062,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -6091,28 +6103,28 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>3</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -6141,28 +6153,28 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>4</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -6191,28 +6203,28 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>5</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -6241,13 +6253,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6265,10 +6277,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -6291,13 +6303,13 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6315,10 +6327,10 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -6341,13 +6353,13 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6365,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -6391,13 +6403,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6415,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -6441,13 +6453,13 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6465,10 +6477,10 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -6491,19 +6503,19 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -6512,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -6541,19 +6553,19 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -6562,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -6591,19 +6603,19 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -6612,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -6641,19 +6653,19 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -6662,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -6691,19 +6703,19 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="B21">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -6712,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -6741,13 +6753,13 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6756,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -6768,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6791,13 +6803,13 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6806,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -6818,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6841,13 +6853,13 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6856,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -6868,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6891,13 +6903,13 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6906,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -6918,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6941,13 +6953,13 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6956,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -6968,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6991,25 +7003,25 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -7041,25 +7053,25 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -7091,25 +7103,25 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -7141,25 +7153,25 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -7191,25 +7203,25 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -7241,13 +7253,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>179</v>
+        <v>199</v>
+      </c>
+      <c r="D32" t="s">
+        <v>199</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7256,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -7271,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -7291,13 +7306,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>199</v>
+      </c>
+      <c r="D33" t="s">
+        <v>199</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7306,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -7321,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -7341,13 +7359,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>199</v>
+      </c>
+      <c r="D34" t="s">
+        <v>199</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7356,7 +7377,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -7371,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -7391,13 +7412,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>199</v>
+      </c>
+      <c r="D35" t="s">
+        <v>199</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7406,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -7421,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -7441,13 +7465,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>199</v>
+      </c>
+      <c r="D36" t="s">
+        <v>199</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7456,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -7471,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -7491,13 +7518,16 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>205</v>
+      </c>
+      <c r="D37" t="s">
+        <v>206</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7509,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -7524,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -7541,13 +7571,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>180</v>
+        <v>205</v>
+      </c>
+      <c r="D38" t="s">
+        <v>206</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7559,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -7574,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -7591,13 +7624,16 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>205</v>
+      </c>
+      <c r="D39" t="s">
+        <v>206</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7609,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -7624,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -7641,13 +7677,16 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>180</v>
+        <v>205</v>
+      </c>
+      <c r="D40" t="s">
+        <v>206</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7659,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -7674,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -7691,13 +7730,16 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B41">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>180</v>
+        <v>205</v>
+      </c>
+      <c r="D41" t="s">
+        <v>206</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7709,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -7724,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -7741,16 +7783,16 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -7774,13 +7816,13 @@
         <v>0</v>
       </c>
       <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
         <v>5</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -7794,16 +7836,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D43" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -7827,13 +7869,13 @@
         <v>0</v>
       </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
         <v>10</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -7847,16 +7889,16 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -7880,13 +7922,13 @@
         <v>0</v>
       </c>
       <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
         <v>15</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -7900,16 +7942,16 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7933,13 +7975,13 @@
         <v>0</v>
       </c>
       <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
         <v>20</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -7953,16 +7995,16 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -7986,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
         <v>30</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -8006,16 +8048,16 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D47" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -8042,13 +8084,13 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -8059,16 +8101,16 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B48">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -8095,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N48">
         <v>0</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -8112,16 +8154,16 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -8148,13 +8190,13 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N49">
         <v>0</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -8165,16 +8207,16 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -8201,13 +8243,13 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -8218,16 +8260,16 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B51">
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D51" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -8254,13 +8296,13 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N51">
         <v>0</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -8271,16 +8313,16 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D52" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -8310,13 +8352,13 @@
         <v>0</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8324,16 +8366,16 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D53" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -8363,13 +8405,13 @@
         <v>0</v>
       </c>
       <c r="N53">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8377,16 +8419,16 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -8416,13 +8458,13 @@
         <v>0</v>
       </c>
       <c r="N54">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -8430,16 +8472,16 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B55">
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D55" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -8469,13 +8511,13 @@
         <v>0</v>
       </c>
       <c r="N55">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -8483,16 +8525,16 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B56">
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D56" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -8522,13 +8564,13 @@
         <v>0</v>
       </c>
       <c r="N56">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -8536,16 +8578,16 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D57" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -8578,27 +8620,27 @@
         <v>0</v>
       </c>
       <c r="O57">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P57">
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D58" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -8631,27 +8673,27 @@
         <v>0</v>
       </c>
       <c r="O58">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P58">
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D59" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -8684,27 +8726,27 @@
         <v>0</v>
       </c>
       <c r="O59">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P59">
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B60">
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -8737,27 +8779,27 @@
         <v>0</v>
       </c>
       <c r="O60">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P60">
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B61">
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D61" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -8790,565 +8832,35 @@
         <v>0</v>
       </c>
       <c r="O61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P61">
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>208</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>208</v>
-      </c>
-      <c r="D62" t="s">
-        <v>208</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>2</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>208</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63" t="s">
-        <v>208</v>
-      </c>
-      <c r="D63" t="s">
-        <v>208</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>4</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>208</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64" t="s">
-        <v>208</v>
-      </c>
-      <c r="D64" t="s">
-        <v>208</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>6</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>208</v>
-      </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s">
-        <v>208</v>
-      </c>
-      <c r="D65" t="s">
-        <v>208</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>8</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>208</v>
-      </c>
-      <c r="B66">
         <v>5</v>
-      </c>
-      <c r="C66" t="s">
-        <v>208</v>
-      </c>
-      <c r="D66" t="s">
-        <v>208</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>12</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>197</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67" t="s">
-        <v>197</v>
-      </c>
-      <c r="D67" t="s">
-        <v>197</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>197</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68" t="s">
-        <v>197</v>
-      </c>
-      <c r="D68" t="s">
-        <v>197</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>197</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="C69" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" t="s">
-        <v>197</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>197</v>
-      </c>
-      <c r="B70">
-        <v>4</v>
-      </c>
-      <c r="C70" t="s">
-        <v>197</v>
-      </c>
-      <c r="D70" t="s">
-        <v>197</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>197</v>
-      </c>
-      <c r="B71">
-        <v>5</v>
-      </c>
-      <c r="C71" t="s">
-        <v>197</v>
-      </c>
-      <c r="D71" t="s">
-        <v>197</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:K41">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:Q61">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:Q71">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Assets/EggRogue/Configs/Excel/EggRogue_Balance.xlsx
+++ b/Assets/EggRogue/Configs/Excel/EggRogue_Balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MiniGameExample\Assets\EggRogue\Configs\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69CFFA4-B8EF-494D-B170-52E5A4BA3BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E692A650-B648-470D-A07A-A5EB71A1499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="225" windowWidth="38640" windowHeight="20715" activeTab="5" xr2:uid="{BD38E421-D0F5-4413-AB74-14A7BC66D52F}"/>
   </bookViews>
@@ -4619,13 +4619,13 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>10</v>
